--- a/data/reports/mapping_sap_procosa_full.xlsx
+++ b/data/reports/mapping_sap_procosa_full.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mappings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run Metadata" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mapeamentos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadados da Execução" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,117 +432,117 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>model_column_number</t>
+          <t>numero_coluna_modelo</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>model_column</t>
+          <t>coluna_modelo</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>client_column_number</t>
+          <t>numero_coluna_cliente</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>client_column</t>
+          <t>coluna_cliente</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>name_confidence</t>
+          <t>confianca_nome</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>name_runner_up_confidence</t>
+          <t>confianca_nome_segunda_melhor</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>name_margin</t>
+          <t>margem_nome</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>data_confidence</t>
+          <t>confianca_dados</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>final_confidence</t>
+          <t>confianca_final</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>method</t>
+          <t>metodo</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>situacao</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>justificativa</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>catalog_name</t>
+          <t>nome_catalogo</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>catalog_coverage</t>
+          <t>cobertura_catalogo</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>catalog_confidence</t>
+          <t>confianca_catalogo</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>llm_data_confidence</t>
+          <t>confianca_dados_ia</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>llm_final_confidence</t>
+          <t>confianca_final_ia</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>decided_by</t>
+          <t>decidido_por</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>supported_by</t>
+          <t>apoiado_por</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>vetoed_by</t>
+          <t>vetado_por</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>reviewer_status</t>
+          <t>parecer_revisor</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>correct_client_column</t>
+          <t>coluna_cliente_correta</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>reviewer_note</t>
+          <t>observacao_revisor</t>
         </is>
       </c>
     </row>
@@ -580,12 +580,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -601,18 +601,18 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>no_mapping_exists</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -652,27 +652,27 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -711,17 +711,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>The header and a row-wise fiscal relationship jointly support this column with a clear lead over alternatives.</t>
+          <t>O cabeçalho e uma relação fiscal verificada linha a linha sustentam juntos esta coluna, com vantagem clara sobre as alternativas.</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -732,12 +732,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>unrecorded</t>
+          <t>nao_registrado</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>resolver + semantic + unrecorded</t>
+          <t>resolvedor_ia + semantico + nao_registrado</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -773,27 +773,27 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -829,27 +829,27 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -885,27 +885,27 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -936,12 +936,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -990,17 +990,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>O resolvedor de IA encontrou evidências favoráveis, mas não escolheu nenhuma coluna; o candidato com o cabeçalho mais forte fica para revisão.</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1011,18 +1011,18 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>no_mapping_exists</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1062,27 +1062,27 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1118,27 +1118,27 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1174,27 +1174,27 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1254,18 +1254,18 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>correto</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -1305,27 +1305,27 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1410,17 +1410,17 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>O resolvedor de IA encontrou evidências favoráveis, mas não escolheu nenhuma coluna; o candidato com o cabeçalho mais forte fica para revisão.</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -1431,18 +1431,18 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>no_mapping_exists</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -1482,27 +1482,27 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>aritmetica</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>semantic + arithmetic</t>
+          <t>semantico + aritmetica</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -1541,17 +1541,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>The header and a row-wise fiscal relationship jointly support this column with a clear lead over alternatives.</t>
+          <t>O cabeçalho e uma relação fiscal verificada linha a linha sustentam juntos esta coluna, com vantagem clara sobre as alternativas.</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>aritmetica</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>resolver + semantic + arithmetic</t>
+          <t>resolvedor_ia + semantico + aritmetica</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -1603,27 +1603,27 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>aritmetica</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>semantic + arithmetic</t>
+          <t>semantico + aritmetica</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -1662,17 +1662,17 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>O resolvedor de IA encontrou evidências favoráveis, mas não escolheu nenhuma coluna; o candidato com o cabeçalho mais forte fica para revisão.</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -1683,18 +1683,18 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>correto</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -1737,17 +1737,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>O resolvedor de IA encontrou evidências favoráveis, mas não escolheu nenhuma coluna; o candidato com o cabeçalho mais forte fica para revisão.</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -1758,18 +1758,18 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>correto</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1858,17 +1858,17 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>O resolvedor de IA encontrou evidências favoráveis, mas não escolheu nenhuma coluna; o candidato com o cabeçalho mais forte fica para revisão.</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -1879,18 +1879,18 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>no_mapping_exists</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -1933,17 +1933,17 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>O resolvedor de IA encontrou evidências favoráveis, mas não escolheu nenhuma coluna; o candidato com o cabeçalho mais forte fica para revisão.</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -1954,18 +1954,18 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>no_mapping_exists</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2029,18 +2029,18 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>no_mapping_exists</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2104,18 +2104,18 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>no_mapping_exists</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -2158,17 +2158,17 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>O resolvedor de IA encontrou evidências favoráveis, mas não escolheu nenhuma coluna; o candidato com o cabeçalho mais forte fica para revisão.</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2179,18 +2179,18 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>no_mapping_exists</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2254,18 +2254,18 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>no_mapping_exists</t>
+          <t>inexistente</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2351,27 +2351,27 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -2410,12 +2410,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2431,18 +2431,18 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>correto</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2506,18 +2506,18 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>correto</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -2622,27 +2622,27 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -2678,17 +2678,17 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>catalog</t>
+          <t>catalogo</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>semantic + catalog</t>
+          <t>semantico + catalogo</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -2748,12 +2748,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -2813,12 +2813,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2834,18 +2834,18 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>correto</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>incorrect</t>
+          <t>incorreto</t>
         </is>
       </c>
       <c r="V38" t="n">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>incorrect</t>
+          <t>incorreto</t>
         </is>
       </c>
       <c r="V39" t="n">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
@@ -3117,17 +3117,17 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>The header and a row-wise fiscal relationship jointly support this column with a clear lead over alternatives.</t>
+          <t>O cabeçalho e uma relação fiscal verificada linha a linha sustentam juntos esta coluna, com vantagem clara sobre as alternativas.</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>aritmetica</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>resolver + semantic + arithmetic</t>
+          <t>resolvedor_ia + semantico + aritmetica</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
@@ -3179,27 +3179,27 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>aritmetica</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>semantic + arithmetic</t>
+          <t>semantico + aritmetica</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -3230,17 +3230,17 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3305,18 +3305,18 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>correto</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3380,18 +3380,18 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>correto</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -3434,17 +3434,17 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>O resolvedor de IA encontrou evidências favoráveis, mas não escolheu nenhuma coluna; o candidato com o cabeçalho mais forte fica para revisão.</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -3491,17 +3491,17 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -3545,17 +3545,17 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>The header and a row-wise fiscal relationship jointly support this column with a clear lead over alternatives.</t>
+          <t>O cabeçalho e uma relação fiscal verificada linha a linha sustentam juntos esta coluna, com vantagem clara sobre as alternativas.</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>aritmetica</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>resolver + semantic + arithmetic</t>
+          <t>resolvedor_ia + semantico + aritmetica</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -3607,27 +3607,27 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>aritmetica</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>semantic + arithmetic</t>
+          <t>semantico + aritmetica</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
@@ -3666,12 +3666,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3687,18 +3687,18 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>correto</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -3738,27 +3738,27 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
@@ -3797,17 +3797,17 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>The header and a row-wise fiscal relationship jointly support this column with a clear lead over alternatives.</t>
+          <t>O cabeçalho e uma relação fiscal verificada linha a linha sustentam juntos esta coluna, com vantagem clara sobre as alternativas.</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>aritmetica</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>resolver + semantic + arithmetic</t>
+          <t>resolvedor_ia + semantico + aritmetica</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -3859,27 +3859,27 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>aritmetica</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>semantic + arithmetic</t>
+          <t>semantico + aritmetica</t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
@@ -3918,17 +3918,17 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>The header and a row-wise fiscal relationship jointly support this column with a clear lead over alternatives.</t>
+          <t>O cabeçalho e uma relação fiscal verificada linha a linha sustentam juntos esta coluna, com vantagem clara sobre as alternativas.</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>aritmetica</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>resolver + semantic + arithmetic</t>
+          <t>resolvedor_ia + semantico + aritmetica</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
@@ -3980,27 +3980,27 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>aritmetica</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>semantic + arithmetic</t>
+          <t>semantico + aritmetica</t>
         </is>
       </c>
       <c r="T56" t="inlineStr"/>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4128,27 +4128,27 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
@@ -4179,17 +4179,17 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -4230,27 +4230,27 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -4289,12 +4289,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4310,18 +4310,18 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>correto</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4448,17 +4448,17 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T66" t="inlineStr"/>
@@ -4567,12 +4567,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4588,12 +4588,12 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T67" t="inlineStr"/>
@@ -4632,12 +4632,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T68" t="inlineStr"/>
@@ -4697,12 +4697,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4718,12 +4718,12 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
@@ -4754,12 +4754,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4846,12 +4846,12 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4892,17 +4892,17 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T74" t="inlineStr"/>
@@ -5003,17 +5003,17 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P75" t="n">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5095,17 +5095,17 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T79" t="inlineStr"/>
@@ -5260,12 +5260,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T80" t="inlineStr"/>
@@ -5317,17 +5317,17 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5392,12 +5392,12 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T82" t="inlineStr"/>
@@ -5428,17 +5428,17 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P83" t="n">
@@ -5479,27 +5479,27 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T84" t="inlineStr"/>
@@ -5535,27 +5535,27 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T85" t="inlineStr"/>
@@ -5586,12 +5586,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5678,17 +5678,17 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5816,17 +5816,17 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P91" t="n">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5954,17 +5954,17 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P94" t="n">
@@ -6000,17 +6000,17 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P95" t="n">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6230,17 +6230,17 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -6276,17 +6276,17 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P101" t="n">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>O resolvedor de IA encontrou evidências favoráveis, mas não escolheu nenhuma coluna; o candidato com o cabeçalho mais forte fica para revisão.</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T102" t="inlineStr"/>
@@ -6387,17 +6387,17 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P103" t="n">
@@ -6433,17 +6433,17 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6525,12 +6525,12 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6571,17 +6571,17 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -6625,12 +6625,12 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -6646,12 +6646,12 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T108" t="inlineStr"/>
@@ -6682,17 +6682,17 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -6757,17 +6757,17 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>family_conflict</t>
+          <t>conflito_tributario</t>
         </is>
       </c>
     </row>
@@ -6805,12 +6805,12 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -6826,17 +6826,17 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>family_conflict</t>
+          <t>conflito_tributario</t>
         </is>
       </c>
     </row>
@@ -6874,17 +6874,17 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>O resolvedor de IA encontrou evidências favoráveis, mas não escolheu nenhuma coluna; o candidato com o cabeçalho mais forte fica para revisão.</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -6895,17 +6895,17 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>family_conflict</t>
+          <t>conflito_tributario</t>
         </is>
       </c>
     </row>
@@ -6943,12 +6943,12 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T113" t="inlineStr"/>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7029,12 +7029,12 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T114" t="inlineStr"/>
@@ -7073,12 +7073,12 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T115" t="inlineStr"/>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>O resolvedor de IA encontrou evidências favoráveis, mas não escolheu nenhuma coluna; o candidato com o cabeçalho mais forte fica para revisão.</t>
         </is>
       </c>
       <c r="P116" t="n">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T116" t="inlineStr"/>
@@ -7203,17 +7203,17 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>O resolvedor de IA encontrou evidências favoráveis, mas não escolheu nenhuma coluna; o candidato com o cabeçalho mais forte fica para revisão.</t>
         </is>
       </c>
       <c r="P117" t="n">
@@ -7224,12 +7224,12 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T117" t="inlineStr"/>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7306,12 +7306,12 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -7352,12 +7352,12 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -7406,17 +7406,17 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>O resolvedor de IA encontrou evidências favoráveis, mas não escolheu nenhuma coluna; o candidato com o cabeçalho mais forte fica para revisão.</t>
         </is>
       </c>
       <c r="P121" t="n">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T121" t="inlineStr"/>
@@ -7471,12 +7471,12 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -7492,18 +7492,18 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T122" t="inlineStr"/>
       <c r="U122" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>correto</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T124" t="inlineStr"/>
@@ -7654,27 +7654,27 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T125" t="inlineStr"/>
@@ -7705,12 +7705,12 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -7751,17 +7751,17 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -7797,12 +7797,12 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -7889,17 +7889,17 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -7964,12 +7964,12 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T131" t="inlineStr"/>
@@ -8000,17 +8000,17 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -8046,17 +8046,17 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P133" t="n">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -8138,17 +8138,17 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P135" t="n">
@@ -8184,17 +8184,17 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P137" t="n">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -8322,12 +8322,12 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -8368,17 +8368,17 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -8414,17 +8414,17 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -8460,17 +8460,17 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -8506,17 +8506,17 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -8552,17 +8552,17 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -8598,17 +8598,17 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P145" t="n">
@@ -8644,17 +8644,17 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P146" t="n">
@@ -8690,17 +8690,17 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P147" t="n">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -8790,12 +8790,12 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -8811,18 +8811,18 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>correto</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
@@ -8857,17 +8857,17 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -8995,17 +8995,17 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -9041,12 +9041,12 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -9133,17 +9133,17 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P156" t="n">
@@ -9179,17 +9179,17 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P157" t="n">
@@ -9225,17 +9225,17 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P158" t="n">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T159" t="inlineStr"/>
@@ -9336,12 +9336,12 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -9382,17 +9382,17 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P161" t="n">
@@ -9436,12 +9436,12 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T162" t="inlineStr"/>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T166" t="inlineStr"/>
@@ -9704,12 +9704,12 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -9725,12 +9725,12 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T167" t="inlineStr"/>
@@ -9761,17 +9761,17 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P168" t="n">
@@ -9807,17 +9807,17 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P169" t="n">
@@ -9861,12 +9861,12 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T170" t="inlineStr"/>
@@ -9926,12 +9926,12 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -9947,12 +9947,12 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T171" t="inlineStr"/>
@@ -9991,12 +9991,12 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T172" t="inlineStr"/>
@@ -10048,12 +10048,12 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -10145,27 +10145,27 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T175" t="inlineStr"/>
@@ -10196,17 +10196,17 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P176" t="n">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>ibs_cbs_cst</t>
+          <t>cst_ibs_cbs</t>
         </is>
       </c>
       <c r="N177" t="n">
@@ -10282,18 +10282,18 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>catalog</t>
+          <t>catalogo</t>
         </is>
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>resolver + semantic + catalog</t>
+          <t>resolvedor_ia + semantico + catalogo</t>
         </is>
       </c>
       <c r="T177" t="inlineStr"/>
       <c r="U177" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>correto</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
@@ -10333,22 +10333,22 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>ibs_cbs_classification</t>
+          <t>cclasstrib</t>
         </is>
       </c>
       <c r="N178" t="n">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>semantic + catalog (agrees)</t>
+          <t>semantico + catalogo (concorda)</t>
         </is>
       </c>
       <c r="T178" t="inlineStr"/>
@@ -10403,12 +10403,12 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -10424,18 +10424,18 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T179" t="inlineStr"/>
       <c r="U179" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>correto</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
@@ -10475,27 +10475,27 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T180" t="inlineStr"/>
@@ -10526,12 +10526,12 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -10572,17 +10572,17 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P182" t="n">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -10664,17 +10664,17 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P184" t="n">
@@ -10715,27 +10715,27 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>aritmetica</t>
         </is>
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>semantic + arithmetic</t>
+          <t>semantico + aritmetica</t>
         </is>
       </c>
       <c r="T185" t="inlineStr"/>
@@ -10766,17 +10766,17 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P186" t="n">
@@ -10820,12 +10820,12 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -10841,12 +10841,12 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T187" t="inlineStr"/>
@@ -10885,12 +10885,12 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T188" t="inlineStr"/>
@@ -10950,12 +10950,12 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -10971,12 +10971,12 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T189" t="inlineStr"/>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -11058,27 +11058,27 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>aritmetica</t>
         </is>
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>semantic + arithmetic</t>
+          <t>semantico + aritmetica</t>
         </is>
       </c>
       <c r="T191" t="inlineStr"/>
@@ -11109,17 +11109,17 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P192" t="n">
@@ -11160,27 +11160,27 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>aritmetica</t>
         </is>
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>semantic + arithmetic</t>
+          <t>semantico + aritmetica</t>
         </is>
       </c>
       <c r="T193" t="inlineStr"/>
@@ -11211,17 +11211,17 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P194" t="n">
@@ -11257,12 +11257,12 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -11311,12 +11311,12 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -11332,12 +11332,12 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T196" t="inlineStr"/>
@@ -11373,27 +11373,27 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T197" t="inlineStr"/>
@@ -11429,27 +11429,27 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T198" t="inlineStr"/>
@@ -11485,27 +11485,27 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T199" t="inlineStr"/>
@@ -11541,27 +11541,27 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T200" t="inlineStr"/>
@@ -11592,12 +11592,12 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -11638,12 +11638,12 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -11730,12 +11730,12 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -11781,17 +11781,17 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>catalog</t>
+          <t>catalogo</t>
         </is>
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>semantic + catalog</t>
+          <t>semantico + catalogo</t>
         </is>
       </c>
       <c r="T205" t="inlineStr"/>
@@ -11851,12 +11851,12 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -11872,12 +11872,12 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T206" t="inlineStr"/>
@@ -11908,17 +11908,17 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P207" t="n">
@@ -11962,12 +11962,12 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -11983,12 +11983,12 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T208" t="inlineStr"/>
@@ -12027,12 +12027,12 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T209" t="inlineStr"/>
@@ -12092,12 +12092,12 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -12113,18 +12113,18 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T210" t="inlineStr"/>
       <c r="U210" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>correto</t>
         </is>
       </c>
       <c r="W210" t="inlineStr">
@@ -12167,12 +12167,12 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -12188,12 +12188,12 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>resolver + semantic</t>
+          <t>resolvedor_ia + semantico</t>
         </is>
       </c>
       <c r="T211" t="inlineStr"/>
@@ -12224,17 +12224,17 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P212" t="n">
@@ -12270,12 +12270,12 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -12321,27 +12321,27 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>arithmetic</t>
+          <t>aritmetica</t>
         </is>
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>semantic + arithmetic</t>
+          <t>semantico + aritmetica</t>
         </is>
       </c>
       <c r="T214" t="inlineStr"/>
@@ -12377,27 +12377,27 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T215" t="inlineStr"/>
@@ -12436,17 +12436,17 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>O resolvedor de IA encontrou evidências favoráveis, mas não escolheu nenhuma coluna; o candidato com o cabeçalho mais forte fica para revisão.</t>
         </is>
       </c>
       <c r="P216" t="n">
@@ -12457,12 +12457,12 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T216" t="inlineStr"/>
@@ -12501,17 +12501,17 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>revisao</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>The resolver found supporting evidence but did not commit to a column; retain the strongest header candidate for review.</t>
+          <t>O resolvedor de IA encontrou evidências favoráveis, mas não escolheu nenhuma coluna; o candidato com o cabeçalho mais forte fica para revisão.</t>
         </is>
       </c>
       <c r="P217" t="n">
@@ -12522,12 +12522,12 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T217" t="inlineStr"/>
@@ -12566,17 +12566,17 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>Distinctive non-zero sample values overlap exactly with this candidate and not with the competing columns.</t>
+          <t>Valores de amostra distintivos e diferentes de zero coincidem exatamente com este candidato, e não com as colunas concorrentes.</t>
         </is>
       </c>
       <c r="P218" t="n">
@@ -12587,12 +12587,12 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>unrecorded</t>
+          <t>nao_registrado</t>
         </is>
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>resolver + semantic + unrecorded</t>
+          <t>resolvedor_ia + semantico + nao_registrado</t>
         </is>
       </c>
       <c r="T218" t="inlineStr"/>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Direito (occurrence 3)</t>
+          <t>Direito (ocorrência 3)</t>
         </is>
       </c>
       <c r="E219" t="n">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>unrecorded</t>
+          <t>nao_registrado</t>
         </is>
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>resolver + semantic + unrecorded</t>
+          <t>resolvedor_ia + semantico + nao_registrado</t>
         </is>
       </c>
       <c r="T219" t="inlineStr"/>
@@ -12688,12 +12688,12 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -12734,12 +12734,12 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -12780,17 +12780,17 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P222" t="n">
@@ -12826,17 +12826,17 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P223" t="n">
@@ -12872,12 +12872,12 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -12918,17 +12918,17 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P225" t="n">
@@ -12964,12 +12964,12 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -13015,27 +13015,27 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>nome</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>aceito</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>Accepted from header similarity with a clear lead over the runner-up.</t>
+          <t>Aceito pela semelhança do cabeçalho, com vantagem clara sobre a segunda melhor opção.</t>
         </is>
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>semantic</t>
+          <t>semantico</t>
         </is>
       </c>
       <c r="T227" t="inlineStr"/>
@@ -13066,17 +13066,17 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>dados</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>no_match</t>
+          <t>sem_correspondencia</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>No candidate had enough combined header and distinctive row evidence; the client export may not contain this model field.</t>
+          <t>Nenhum candidato reuniu evidência suficiente de cabeçalho e de linhas distintivas; a exportação do cliente pode não conter este campo do modelo.</t>
         </is>
       </c>
       <c r="P228" t="n">
@@ -13097,35 +13097,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>key</t>
+          <t>chave</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>valor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mapping_schema_version</t>
+          <t>versao_esquema_mapeamento</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>generated_at_utc</t>
+          <t>gerado_em_utc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -13137,7 +13137,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>prompt_version</t>
+          <t>versao_prompt</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -13149,7 +13149,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>client_file</t>
+          <t>arquivo_cliente</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -13161,7 +13161,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>client_sha256</t>
+          <t>sha256_cliente</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -13173,7 +13173,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>model_file</t>
+          <t>arquivo_modelo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -13185,7 +13185,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>model_sha256</t>
+          <t>sha256_modelo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -13197,7 +13197,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>client_sheet</t>
+          <t>aba_cliente</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -13209,7 +13209,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>model_sheet</t>
+          <t>aba_modelo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -13221,7 +13221,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>client_header_row</t>
+          <t>linha_cabecalho_cliente</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -13231,7 +13231,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>model_header_row</t>
+          <t>linha_cabecalho_modelo</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -13241,7 +13241,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>embedding_model</t>
+          <t>modelo_embedding</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -13253,7 +13253,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>llm_model</t>
+          <t>modelo_ia</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -13265,7 +13265,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>name_threshold</t>
+          <t>limiar_nome</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -13275,7 +13275,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>name_margin</t>
+          <t>margem_minima_nome</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -13285,7 +13285,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>final_threshold</t>
+          <t>limiar_final</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -13295,7 +13295,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>candidate_count</t>
+          <t>quantidade_candidatos</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -13305,7 +13305,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>sample_size</t>
+          <t>tamanho_amostra</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -13315,13 +13315,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>reference_manifest_sha256</t>
+          <t>sha256_manifesto_referencia</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>c4e2106d5da8d59bb0b3ba304cd6c68500a22be3972e6bce81c122fc29a677f1</t>
         </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>migrado_da_versao_esquema</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
